--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332740</v>
+        <v>124332737</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687507</v>
+        <v>687553</v>
       </c>
       <c r="R3" t="n">
-        <v>7096131</v>
+        <v>7096117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332737</v>
+        <v>124332740</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687553</v>
+        <v>687507</v>
       </c>
       <c r="R4" t="n">
-        <v>7096117</v>
+        <v>7096131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332738</v>
+        <v>124332769</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,16 +1057,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687514</v>
+        <v>687515</v>
       </c>
       <c r="R5" t="n">
-        <v>7096131</v>
+        <v>7096129</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,6 +1120,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1255,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332742</v>
+        <v>124332731</v>
       </c>
       <c r="B7" t="n">
         <v>92321</v>
@@ -1299,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687577</v>
+        <v>687535</v>
       </c>
       <c r="R7" t="n">
-        <v>7096121</v>
+        <v>7096147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332744</v>
+        <v>124332742</v>
       </c>
       <c r="B8" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687633</v>
+        <v>687577</v>
       </c>
       <c r="R8" t="n">
-        <v>7096189</v>
+        <v>7096121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332771</v>
+        <v>124332782</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1507,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1534,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687471</v>
+        <v>687628</v>
       </c>
       <c r="R9" t="n">
-        <v>7096139</v>
+        <v>7096143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332736</v>
+        <v>124332776</v>
       </c>
       <c r="B10" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1645,16 +1649,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687498</v>
+        <v>687475</v>
       </c>
       <c r="R10" t="n">
-        <v>7096136</v>
+        <v>7096137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,6 +1712,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1723,7 +1731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332769</v>
+        <v>124332787</v>
       </c>
       <c r="B11" t="n">
         <v>92321</v>
@@ -1770,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687515</v>
+        <v>687548</v>
       </c>
       <c r="R11" t="n">
-        <v>7096129</v>
+        <v>7096130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332760</v>
+        <v>124332738</v>
       </c>
       <c r="B12" t="n">
-        <v>92293</v>
+        <v>92285</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1863,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1887,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687631</v>
+        <v>687514</v>
       </c>
       <c r="R12" t="n">
-        <v>7096155</v>
+        <v>7096131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332731</v>
+        <v>124332758</v>
       </c>
       <c r="B13" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1983,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2003,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687535</v>
+        <v>687553</v>
       </c>
       <c r="R13" t="n">
-        <v>7096147</v>
+        <v>7096128</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,6 +2065,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332782</v>
+        <v>124332732</v>
       </c>
       <c r="B15" t="n">
-        <v>90051</v>
+        <v>92285</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,21 +2216,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2229,19 +2238,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687628</v>
+        <v>687561</v>
       </c>
       <c r="R15" t="n">
-        <v>7096143</v>
+        <v>7096151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2292,7 +2298,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2311,7 +2316,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332787</v>
+        <v>124332747</v>
       </c>
       <c r="B16" t="n">
         <v>92321</v>
@@ -2349,19 +2354,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687548</v>
+        <v>687633</v>
       </c>
       <c r="R16" t="n">
-        <v>7096130</v>
+        <v>7096156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,7 +2414,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2551,7 +2552,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332747</v>
+        <v>124332771</v>
       </c>
       <c r="B18" t="n">
         <v>92321</v>
@@ -2589,16 +2590,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687633</v>
+        <v>687471</v>
       </c>
       <c r="R18" t="n">
-        <v>7096156</v>
+        <v>7096139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,6 +2653,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2667,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332730</v>
+        <v>124332772</v>
       </c>
       <c r="B19" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,21 +2688,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2705,16 +2710,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687548</v>
+        <v>687611</v>
       </c>
       <c r="R19" t="n">
-        <v>7096159</v>
+        <v>7096125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,6 +2773,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2783,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332758</v>
+        <v>124332744</v>
       </c>
       <c r="B20" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2799,21 +2808,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2827,10 +2836,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R20" t="n">
-        <v>7096128</v>
+        <v>7096189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,7 +2890,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2908,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332735</v>
+        <v>124332760</v>
       </c>
       <c r="B21" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,25 +2920,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2944,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687625</v>
+        <v>687631</v>
       </c>
       <c r="R21" t="n">
-        <v>7096144</v>
+        <v>7096155</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,10 +3024,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332772</v>
+        <v>124332730</v>
       </c>
       <c r="B22" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,21 +3040,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3054,19 +3062,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687611</v>
+        <v>687548</v>
       </c>
       <c r="R22" t="n">
-        <v>7096125</v>
+        <v>7096159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,7 +3122,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3136,7 +3140,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332776</v>
+        <v>124332735</v>
       </c>
       <c r="B23" t="n">
         <v>92321</v>
@@ -3174,19 +3178,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687475</v>
+        <v>687625</v>
       </c>
       <c r="R23" t="n">
-        <v>7096137</v>
+        <v>7096144</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3237,7 +3238,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332732</v>
+        <v>124332736</v>
       </c>
       <c r="B24" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687561</v>
+        <v>687498</v>
       </c>
       <c r="R24" t="n">
-        <v>7096151</v>
+        <v>7096136</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332737</v>
+        <v>124332736</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687553</v>
+        <v>687498</v>
       </c>
       <c r="R3" t="n">
-        <v>7096117</v>
+        <v>7096136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332740</v>
+        <v>124332760</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687507</v>
+        <v>687631</v>
       </c>
       <c r="R4" t="n">
-        <v>7096131</v>
+        <v>7096155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332769</v>
+        <v>124332745</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,19 +1057,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687515</v>
+        <v>687633</v>
       </c>
       <c r="R5" t="n">
-        <v>7096129</v>
+        <v>7096189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1117,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332779</v>
+        <v>124332758</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,19 +1173,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687626</v>
+        <v>687553</v>
       </c>
       <c r="R6" t="n">
-        <v>7096139</v>
+        <v>7096128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332731</v>
+        <v>124332780</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1297,16 +1290,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687535</v>
+        <v>687681</v>
       </c>
       <c r="R7" t="n">
-        <v>7096147</v>
+        <v>7096188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,6 +1353,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332782</v>
+        <v>124332779</v>
       </c>
       <c r="B9" t="n">
-        <v>90051</v>
+        <v>92287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,21 +1504,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1538,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687628</v>
+        <v>687626</v>
       </c>
       <c r="R9" t="n">
-        <v>7096143</v>
+        <v>7096139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332776</v>
+        <v>124332730</v>
       </c>
       <c r="B10" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1624,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1649,19 +1646,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687475</v>
+        <v>687548</v>
       </c>
       <c r="R10" t="n">
-        <v>7096137</v>
+        <v>7096159</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1706,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332787</v>
+        <v>124332782</v>
       </c>
       <c r="B11" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1740,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687548</v>
+        <v>687628</v>
       </c>
       <c r="R11" t="n">
-        <v>7096130</v>
+        <v>7096143</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1851,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332738</v>
+        <v>124332771</v>
       </c>
       <c r="B12" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1860,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1889,16 +1882,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687514</v>
+        <v>687471</v>
       </c>
       <c r="R12" t="n">
-        <v>7096131</v>
+        <v>7096139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,6 +1945,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332758</v>
+        <v>124332787</v>
       </c>
       <c r="B13" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,21 +1980,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2005,16 +2002,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687553</v>
+        <v>687548</v>
       </c>
       <c r="R13" t="n">
-        <v>7096128</v>
+        <v>7096130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332745</v>
+        <v>124332744</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2200,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332732</v>
+        <v>124332735</v>
       </c>
       <c r="B15" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687561</v>
+        <v>687625</v>
       </c>
       <c r="R15" t="n">
-        <v>7096151</v>
+        <v>7096144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332747</v>
+        <v>124332772</v>
       </c>
       <c r="B16" t="n">
         <v>92321</v>
@@ -2354,16 +2354,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687633</v>
+        <v>687611</v>
       </c>
       <c r="R16" t="n">
-        <v>7096156</v>
+        <v>7096125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,6 +2417,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2432,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332780</v>
+        <v>124332738</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,21 +2452,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2470,19 +2474,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687681</v>
+        <v>687514</v>
       </c>
       <c r="R17" t="n">
-        <v>7096188</v>
+        <v>7096131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2533,7 +2534,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332771</v>
+        <v>124332747</v>
       </c>
       <c r="B18" t="n">
         <v>92321</v>
@@ -2590,19 +2590,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687471</v>
+        <v>687633</v>
       </c>
       <c r="R18" t="n">
-        <v>7096139</v>
+        <v>7096156</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2653,7 +2650,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332772</v>
+        <v>124332740</v>
       </c>
       <c r="B19" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2710,19 +2706,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687611</v>
+        <v>687507</v>
       </c>
       <c r="R19" t="n">
-        <v>7096125</v>
+        <v>7096131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2773,7 +2766,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2792,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332744</v>
+        <v>124332769</v>
       </c>
       <c r="B20" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2808,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2830,16 +2822,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687633</v>
+        <v>687515</v>
       </c>
       <c r="R20" t="n">
-        <v>7096189</v>
+        <v>7096129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2890,6 +2885,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2908,10 +2904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332760</v>
+        <v>124332731</v>
       </c>
       <c r="B21" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2920,25 +2916,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2952,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687631</v>
+        <v>687535</v>
       </c>
       <c r="R21" t="n">
-        <v>7096155</v>
+        <v>7096147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3024,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332730</v>
+        <v>124332776</v>
       </c>
       <c r="B22" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3040,21 +3036,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3062,16 +3058,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687548</v>
+        <v>687475</v>
       </c>
       <c r="R22" t="n">
-        <v>7096159</v>
+        <v>7096137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3122,6 +3121,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332735</v>
+        <v>124332732</v>
       </c>
       <c r="B23" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687625</v>
+        <v>687561</v>
       </c>
       <c r="R23" t="n">
-        <v>7096144</v>
+        <v>7096151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332736</v>
+        <v>124332737</v>
       </c>
       <c r="B24" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687498</v>
+        <v>687553</v>
       </c>
       <c r="R24" t="n">
-        <v>7096136</v>
+        <v>7096117</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332736</v>
+        <v>124332747</v>
       </c>
       <c r="B3" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687498</v>
+        <v>687633</v>
       </c>
       <c r="R3" t="n">
-        <v>7096136</v>
+        <v>7096156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332760</v>
+        <v>124332730</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>92285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687631</v>
+        <v>687548</v>
       </c>
       <c r="R4" t="n">
-        <v>7096155</v>
+        <v>7096159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332745</v>
+        <v>124332735</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687633</v>
+        <v>687625</v>
       </c>
       <c r="R5" t="n">
-        <v>7096189</v>
+        <v>7096144</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332758</v>
+        <v>124332732</v>
       </c>
       <c r="B6" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687553</v>
+        <v>687561</v>
       </c>
       <c r="R6" t="n">
-        <v>7096128</v>
+        <v>7096151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332780</v>
+        <v>124332760</v>
       </c>
       <c r="B7" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,19 +1289,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687681</v>
+        <v>687631</v>
       </c>
       <c r="R7" t="n">
-        <v>7096188</v>
+        <v>7096155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1349,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332742</v>
+        <v>124332771</v>
       </c>
       <c r="B8" t="n">
         <v>92321</v>
@@ -1410,16 +1405,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687577</v>
+        <v>687471</v>
       </c>
       <c r="R8" t="n">
-        <v>7096121</v>
+        <v>7096139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,6 +1468,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1488,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332779</v>
+        <v>124332769</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1535,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687626</v>
+        <v>687515</v>
       </c>
       <c r="R9" t="n">
-        <v>7096139</v>
+        <v>7096129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332730</v>
+        <v>124332740</v>
       </c>
       <c r="B10" t="n">
         <v>92285</v>
@@ -1652,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687548</v>
+        <v>687507</v>
       </c>
       <c r="R10" t="n">
-        <v>7096159</v>
+        <v>7096131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,7 +1843,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332771</v>
+        <v>124332742</v>
       </c>
       <c r="B12" t="n">
         <v>92321</v>
@@ -1882,19 +1881,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687471</v>
+        <v>687577</v>
       </c>
       <c r="R12" t="n">
-        <v>7096139</v>
+        <v>7096121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1964,7 +1959,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332787</v>
+        <v>124332731</v>
       </c>
       <c r="B13" t="n">
         <v>92321</v>
@@ -2002,19 +1997,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687548</v>
+        <v>687535</v>
       </c>
       <c r="R13" t="n">
-        <v>7096130</v>
+        <v>7096147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2057,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2084,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332744</v>
+        <v>124332758</v>
       </c>
       <c r="B14" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,21 +2091,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2128,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687633</v>
+        <v>687553</v>
       </c>
       <c r="R14" t="n">
-        <v>7096189</v>
+        <v>7096128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,6 +2173,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2200,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332735</v>
+        <v>124332787</v>
       </c>
       <c r="B15" t="n">
         <v>92321</v>
@@ -2238,16 +2230,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687625</v>
+        <v>687548</v>
       </c>
       <c r="R15" t="n">
-        <v>7096144</v>
+        <v>7096130</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,6 +2293,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332772</v>
+        <v>124332736</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2354,19 +2350,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687611</v>
+        <v>687498</v>
       </c>
       <c r="R16" t="n">
-        <v>7096125</v>
+        <v>7096136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2410,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2436,10 +2428,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332738</v>
+        <v>124332779</v>
       </c>
       <c r="B17" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,21 +2444,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2474,16 +2466,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687514</v>
+        <v>687626</v>
       </c>
       <c r="R17" t="n">
-        <v>7096131</v>
+        <v>7096139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,6 +2529,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2552,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332747</v>
+        <v>124332744</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2568,21 +2564,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2599,7 +2595,7 @@
         <v>687633</v>
       </c>
       <c r="R18" t="n">
-        <v>7096156</v>
+        <v>7096189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332740</v>
+        <v>124332738</v>
       </c>
       <c r="B19" t="n">
         <v>92285</v>
@@ -2712,7 +2708,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687507</v>
+        <v>687514</v>
       </c>
       <c r="R19" t="n">
         <v>7096131</v>
@@ -2784,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332769</v>
+        <v>124332780</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2831,10 +2827,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687515</v>
+        <v>687681</v>
       </c>
       <c r="R20" t="n">
-        <v>7096129</v>
+        <v>7096188</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,7 +2900,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332731</v>
+        <v>124332772</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2942,16 +2938,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687535</v>
+        <v>687611</v>
       </c>
       <c r="R21" t="n">
-        <v>7096147</v>
+        <v>7096125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3002,6 +3001,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332776</v>
+        <v>124332737</v>
       </c>
       <c r="B22" t="n">
         <v>92321</v>
@@ -3058,19 +3058,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687475</v>
+        <v>687553</v>
       </c>
       <c r="R22" t="n">
-        <v>7096137</v>
+        <v>7096117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3121,7 +3118,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332732</v>
+        <v>124332776</v>
       </c>
       <c r="B23" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,21 +3152,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3178,16 +3174,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687561</v>
+        <v>687475</v>
       </c>
       <c r="R23" t="n">
-        <v>7096151</v>
+        <v>7096137</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332737</v>
+        <v>124332745</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R24" t="n">
-        <v>7096117</v>
+        <v>7096189</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332747</v>
+        <v>124332742</v>
       </c>
       <c r="B3" t="n">
         <v>92321</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687633</v>
+        <v>687577</v>
       </c>
       <c r="R3" t="n">
-        <v>7096156</v>
+        <v>7096121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332730</v>
+        <v>124332787</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,6 +941,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
@@ -950,7 +953,7 @@
         <v>687548</v>
       </c>
       <c r="R4" t="n">
-        <v>7096159</v>
+        <v>7096130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332732</v>
+        <v>124332747</v>
       </c>
       <c r="B6" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687561</v>
+        <v>687633</v>
       </c>
       <c r="R6" t="n">
-        <v>7096151</v>
+        <v>7096156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332760</v>
+        <v>124332731</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1295,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687631</v>
+        <v>687535</v>
       </c>
       <c r="R7" t="n">
-        <v>7096155</v>
+        <v>7096147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332771</v>
+        <v>124332736</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,19 +1409,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687471</v>
+        <v>687498</v>
       </c>
       <c r="R8" t="n">
-        <v>7096139</v>
+        <v>7096136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1469,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332769</v>
+        <v>124332738</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,19 +1525,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687515</v>
+        <v>687514</v>
       </c>
       <c r="R9" t="n">
-        <v>7096129</v>
+        <v>7096131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1585,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1723,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332782</v>
+        <v>124332780</v>
       </c>
       <c r="B11" t="n">
-        <v>90051</v>
+        <v>92309</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,21 +1735,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1770,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687628</v>
+        <v>687681</v>
       </c>
       <c r="R11" t="n">
-        <v>7096143</v>
+        <v>7096188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332742</v>
+        <v>124332782</v>
       </c>
       <c r="B12" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1855,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1881,16 +1877,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687577</v>
+        <v>687628</v>
       </c>
       <c r="R12" t="n">
-        <v>7096121</v>
+        <v>7096143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,6 +1940,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332731</v>
+        <v>124332779</v>
       </c>
       <c r="B13" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1997,16 +1997,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687535</v>
+        <v>687626</v>
       </c>
       <c r="R13" t="n">
-        <v>7096147</v>
+        <v>7096139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,6 +2060,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332758</v>
+        <v>124332760</v>
       </c>
       <c r="B14" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,25 +2091,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2119,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687553</v>
+        <v>687631</v>
       </c>
       <c r="R14" t="n">
-        <v>7096128</v>
+        <v>7096155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2173,7 +2177,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332787</v>
+        <v>124332745</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2230,19 +2233,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687548</v>
+        <v>687633</v>
       </c>
       <c r="R15" t="n">
-        <v>7096130</v>
+        <v>7096189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2293,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332736</v>
+        <v>124332772</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2327,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2350,16 +2349,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687498</v>
+        <v>687611</v>
       </c>
       <c r="R16" t="n">
-        <v>7096136</v>
+        <v>7096125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,6 +2412,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332779</v>
+        <v>124332758</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2444,21 +2447,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2466,19 +2469,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687626</v>
+        <v>687553</v>
       </c>
       <c r="R17" t="n">
-        <v>7096139</v>
+        <v>7096128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332744</v>
+        <v>124332769</v>
       </c>
       <c r="B18" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,21 +2564,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2586,16 +2586,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687633</v>
+        <v>687515</v>
       </c>
       <c r="R18" t="n">
-        <v>7096189</v>
+        <v>7096129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2646,6 +2649,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2664,7 +2668,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332738</v>
+        <v>124332730</v>
       </c>
       <c r="B19" t="n">
         <v>92285</v>
@@ -2708,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687514</v>
+        <v>687548</v>
       </c>
       <c r="R19" t="n">
-        <v>7096131</v>
+        <v>7096159</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2780,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332780</v>
+        <v>124332732</v>
       </c>
       <c r="B20" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2818,19 +2822,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687681</v>
+        <v>687561</v>
       </c>
       <c r="R20" t="n">
-        <v>7096188</v>
+        <v>7096151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,7 +2882,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332772</v>
+        <v>124332737</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2938,19 +2938,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687611</v>
+        <v>687553</v>
       </c>
       <c r="R21" t="n">
-        <v>7096125</v>
+        <v>7096117</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3001,7 +2998,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3020,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332737</v>
+        <v>124332744</v>
       </c>
       <c r="B22" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,21 +3032,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3064,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R22" t="n">
-        <v>7096117</v>
+        <v>7096189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332745</v>
+        <v>124332771</v>
       </c>
       <c r="B24" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3294,16 +3290,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687633</v>
+        <v>687471</v>
       </c>
       <c r="R24" t="n">
-        <v>7096189</v>
+        <v>7096139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3354,6 +3353,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332742</v>
+        <v>124332738</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687577</v>
+        <v>687514</v>
       </c>
       <c r="R3" t="n">
-        <v>7096121</v>
+        <v>7096131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332787</v>
+        <v>124332769</v>
       </c>
       <c r="B4" t="n">
         <v>92321</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687548</v>
+        <v>687515</v>
       </c>
       <c r="R4" t="n">
-        <v>7096130</v>
+        <v>7096129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332735</v>
+        <v>124332731</v>
       </c>
       <c r="B5" t="n">
         <v>92321</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687625</v>
+        <v>687535</v>
       </c>
       <c r="R5" t="n">
-        <v>7096144</v>
+        <v>7096147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332747</v>
+        <v>124332780</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,16 +1177,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687633</v>
+        <v>687681</v>
       </c>
       <c r="R6" t="n">
-        <v>7096156</v>
+        <v>7096188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,6 +1240,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332731</v>
+        <v>124332732</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687535</v>
+        <v>687561</v>
       </c>
       <c r="R7" t="n">
-        <v>7096147</v>
+        <v>7096151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332736</v>
+        <v>124332787</v>
       </c>
       <c r="B8" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,16 +1413,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687498</v>
+        <v>687548</v>
       </c>
       <c r="R8" t="n">
-        <v>7096136</v>
+        <v>7096130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,6 +1476,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332738</v>
+        <v>124332742</v>
       </c>
       <c r="B9" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1511,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687514</v>
+        <v>687577</v>
       </c>
       <c r="R9" t="n">
-        <v>7096131</v>
+        <v>7096121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332740</v>
+        <v>124332747</v>
       </c>
       <c r="B10" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687507</v>
+        <v>687633</v>
       </c>
       <c r="R10" t="n">
-        <v>7096131</v>
+        <v>7096156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332780</v>
+        <v>124332735</v>
       </c>
       <c r="B11" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1757,19 +1765,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687681</v>
+        <v>687625</v>
       </c>
       <c r="R11" t="n">
-        <v>7096188</v>
+        <v>7096144</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1825,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1839,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332782</v>
+        <v>124332737</v>
       </c>
       <c r="B12" t="n">
-        <v>90051</v>
+        <v>92321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1877,19 +1881,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687628</v>
+        <v>687553</v>
       </c>
       <c r="R12" t="n">
-        <v>7096143</v>
+        <v>7096117</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332779</v>
+        <v>124332736</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1997,19 +1997,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687626</v>
+        <v>687498</v>
       </c>
       <c r="R13" t="n">
-        <v>7096139</v>
+        <v>7096136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2057,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332760</v>
+        <v>124332776</v>
       </c>
       <c r="B14" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,25 +2087,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2117,16 +2113,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687631</v>
+        <v>687475</v>
       </c>
       <c r="R14" t="n">
-        <v>7096155</v>
+        <v>7096137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,6 +2176,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332745</v>
+        <v>124332782</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>90051</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2233,16 +2233,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687633</v>
+        <v>687628</v>
       </c>
       <c r="R15" t="n">
-        <v>7096189</v>
+        <v>7096143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,6 +2296,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2311,10 +2315,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332772</v>
+        <v>124332744</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2327,21 +2331,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2349,19 +2353,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687611</v>
+        <v>687633</v>
       </c>
       <c r="R16" t="n">
-        <v>7096125</v>
+        <v>7096189</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,7 +2413,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332758</v>
+        <v>124332771</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2469,16 +2469,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687553</v>
+        <v>687471</v>
       </c>
       <c r="R17" t="n">
-        <v>7096128</v>
+        <v>7096139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2548,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332769</v>
+        <v>124332760</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2560,25 +2563,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2586,19 +2589,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687515</v>
+        <v>687631</v>
       </c>
       <c r="R18" t="n">
-        <v>7096129</v>
+        <v>7096155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2649,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2668,7 +2667,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332730</v>
+        <v>124332740</v>
       </c>
       <c r="B19" t="n">
         <v>92285</v>
@@ -2712,10 +2711,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687548</v>
+        <v>687507</v>
       </c>
       <c r="R19" t="n">
-        <v>7096159</v>
+        <v>7096131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2784,10 +2783,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332732</v>
+        <v>124332745</v>
       </c>
       <c r="B20" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2799,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2828,10 +2827,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687561</v>
+        <v>687633</v>
       </c>
       <c r="R20" t="n">
-        <v>7096151</v>
+        <v>7096189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2900,10 +2899,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332737</v>
+        <v>124332758</v>
       </c>
       <c r="B21" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,21 +2915,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2947,7 +2946,7 @@
         <v>687553</v>
       </c>
       <c r="R21" t="n">
-        <v>7096117</v>
+        <v>7096128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2998,6 +2997,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332744</v>
+        <v>124332779</v>
       </c>
       <c r="B22" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3054,16 +3054,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687633</v>
+        <v>687626</v>
       </c>
       <c r="R22" t="n">
-        <v>7096189</v>
+        <v>7096139</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,6 +3117,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3132,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332776</v>
+        <v>124332730</v>
       </c>
       <c r="B23" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,21 +3152,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3170,19 +3174,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687475</v>
+        <v>687548</v>
       </c>
       <c r="R23" t="n">
-        <v>7096137</v>
+        <v>7096159</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,7 +3234,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332771</v>
+        <v>124332772</v>
       </c>
       <c r="B24" t="n">
         <v>92321</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687471</v>
+        <v>687611</v>
       </c>
       <c r="R24" t="n">
-        <v>7096139</v>
+        <v>7096125</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -2667,10 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332740</v>
+        <v>124332758</v>
       </c>
       <c r="B19" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687507</v>
+        <v>687553</v>
       </c>
       <c r="R19" t="n">
-        <v>7096131</v>
+        <v>7096128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,6 +2765,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2783,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332745</v>
+        <v>124332740</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2799,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2827,10 +2828,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687633</v>
+        <v>687507</v>
       </c>
       <c r="R20" t="n">
-        <v>7096189</v>
+        <v>7096131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332758</v>
+        <v>124332745</v>
       </c>
       <c r="B21" t="n">
-        <v>92309</v>
+        <v>92287</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2915,21 +2916,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2943,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R21" t="n">
-        <v>7096128</v>
+        <v>7096189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,7 +2998,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332738</v>
+        <v>124332780</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,16 +825,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687514</v>
+        <v>687681</v>
       </c>
       <c r="R3" t="n">
-        <v>7096131</v>
+        <v>7096188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332769</v>
+        <v>124332782</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687515</v>
+        <v>687628</v>
       </c>
       <c r="R4" t="n">
-        <v>7096129</v>
+        <v>7096143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332731</v>
+        <v>124332738</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687535</v>
+        <v>687514</v>
       </c>
       <c r="R5" t="n">
-        <v>7096147</v>
+        <v>7096131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332780</v>
+        <v>124332744</v>
       </c>
       <c r="B6" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,19 +1181,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687681</v>
+        <v>687633</v>
       </c>
       <c r="R6" t="n">
-        <v>7096188</v>
+        <v>7096189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1241,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332732</v>
+        <v>124332747</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687561</v>
+        <v>687633</v>
       </c>
       <c r="R7" t="n">
-        <v>7096151</v>
+        <v>7096156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332787</v>
+        <v>124332736</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1413,19 +1413,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687548</v>
+        <v>687498</v>
       </c>
       <c r="R8" t="n">
-        <v>7096130</v>
+        <v>7096136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1473,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1495,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332742</v>
+        <v>124332730</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,21 +1507,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1539,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687577</v>
+        <v>687548</v>
       </c>
       <c r="R9" t="n">
-        <v>7096121</v>
+        <v>7096159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332747</v>
+        <v>124332742</v>
       </c>
       <c r="B10" t="n">
         <v>92321</v>
@@ -1655,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687633</v>
+        <v>687577</v>
       </c>
       <c r="R10" t="n">
-        <v>7096156</v>
+        <v>7096121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,7 +1723,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332735</v>
+        <v>124332776</v>
       </c>
       <c r="B11" t="n">
         <v>92321</v>
@@ -1765,16 +1761,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687625</v>
+        <v>687475</v>
       </c>
       <c r="R11" t="n">
-        <v>7096144</v>
+        <v>7096137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,6 +1824,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332737</v>
+        <v>124332779</v>
       </c>
       <c r="B12" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1881,16 +1881,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687553</v>
+        <v>687626</v>
       </c>
       <c r="R12" t="n">
-        <v>7096117</v>
+        <v>7096139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,6 +1944,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332736</v>
+        <v>124332737</v>
       </c>
       <c r="B13" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2003,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687498</v>
+        <v>687553</v>
       </c>
       <c r="R13" t="n">
-        <v>7096136</v>
+        <v>7096117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2075,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332776</v>
+        <v>124332740</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2113,19 +2117,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687475</v>
+        <v>687507</v>
       </c>
       <c r="R14" t="n">
-        <v>7096137</v>
+        <v>7096131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2177,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332782</v>
+        <v>124332769</v>
       </c>
       <c r="B15" t="n">
-        <v>90051</v>
+        <v>92321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687628</v>
+        <v>687515</v>
       </c>
       <c r="R15" t="n">
-        <v>7096143</v>
+        <v>7096129</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332744</v>
+        <v>124332772</v>
       </c>
       <c r="B16" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,21 +2331,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2353,16 +2353,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687633</v>
+        <v>687611</v>
       </c>
       <c r="R16" t="n">
-        <v>7096189</v>
+        <v>7096125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2413,6 +2416,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332771</v>
+        <v>124332732</v>
       </c>
       <c r="B17" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,21 +2451,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2469,19 +2473,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687471</v>
+        <v>687561</v>
       </c>
       <c r="R17" t="n">
-        <v>7096139</v>
+        <v>7096151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2533,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332760</v>
+        <v>124332758</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687631</v>
+        <v>687553</v>
       </c>
       <c r="R18" t="n">
-        <v>7096155</v>
+        <v>7096128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,6 +2649,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2667,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332758</v>
+        <v>124332771</v>
       </c>
       <c r="B19" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2705,16 +2706,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687553</v>
+        <v>687471</v>
       </c>
       <c r="R19" t="n">
-        <v>7096128</v>
+        <v>7096139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2784,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332740</v>
+        <v>124332787</v>
       </c>
       <c r="B20" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2804,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2822,16 +2826,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687507</v>
+        <v>687548</v>
       </c>
       <c r="R20" t="n">
-        <v>7096131</v>
+        <v>7096130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2882,6 +2889,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2908,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332745</v>
+        <v>124332731</v>
       </c>
       <c r="B21" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,21 +2924,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2944,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687633</v>
+        <v>687535</v>
       </c>
       <c r="R21" t="n">
-        <v>7096189</v>
+        <v>7096147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,7 +3024,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332779</v>
+        <v>124332745</v>
       </c>
       <c r="B22" t="n">
         <v>92287</v>
@@ -3054,19 +3062,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687626</v>
+        <v>687633</v>
       </c>
       <c r="R22" t="n">
-        <v>7096139</v>
+        <v>7096189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,7 +3122,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332730</v>
+        <v>124332760</v>
       </c>
       <c r="B23" t="n">
-        <v>92285</v>
+        <v>92293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,25 +3152,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3180,10 +3184,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687548</v>
+        <v>687631</v>
       </c>
       <c r="R23" t="n">
-        <v>7096159</v>
+        <v>7096155</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,7 +3256,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332772</v>
+        <v>124332735</v>
       </c>
       <c r="B24" t="n">
         <v>92321</v>
@@ -3290,19 +3294,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687611</v>
+        <v>687625</v>
       </c>
       <c r="R24" t="n">
-        <v>7096125</v>
+        <v>7096144</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3353,7 +3354,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332780</v>
+        <v>124332742</v>
       </c>
       <c r="B3" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,19 +825,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687681</v>
+        <v>687577</v>
       </c>
       <c r="R3" t="n">
-        <v>7096188</v>
+        <v>7096121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1143,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332744</v>
+        <v>124332745</v>
       </c>
       <c r="B6" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1259,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332747</v>
+        <v>124332744</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1306,7 +1302,7 @@
         <v>687633</v>
       </c>
       <c r="R7" t="n">
-        <v>7096156</v>
+        <v>7096189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332736</v>
+        <v>124332735</v>
       </c>
       <c r="B8" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1419,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687498</v>
+        <v>687625</v>
       </c>
       <c r="R8" t="n">
-        <v>7096136</v>
+        <v>7096144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332730</v>
+        <v>124332780</v>
       </c>
       <c r="B9" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,16 +1525,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687548</v>
+        <v>687681</v>
       </c>
       <c r="R9" t="n">
-        <v>7096159</v>
+        <v>7096188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,6 +1588,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332742</v>
+        <v>124332731</v>
       </c>
       <c r="B10" t="n">
         <v>92321</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687577</v>
+        <v>687535</v>
       </c>
       <c r="R10" t="n">
-        <v>7096121</v>
+        <v>7096147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332776</v>
+        <v>124332787</v>
       </c>
       <c r="B11" t="n">
         <v>92321</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687475</v>
+        <v>687548</v>
       </c>
       <c r="R11" t="n">
-        <v>7096137</v>
+        <v>7096130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332779</v>
+        <v>124332732</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1881,19 +1881,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687626</v>
+        <v>687561</v>
       </c>
       <c r="R12" t="n">
-        <v>7096139</v>
+        <v>7096151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1963,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332737</v>
+        <v>124332736</v>
       </c>
       <c r="B13" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2007,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687553</v>
+        <v>687498</v>
       </c>
       <c r="R13" t="n">
-        <v>7096117</v>
+        <v>7096136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2195,7 +2191,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332769</v>
+        <v>124332737</v>
       </c>
       <c r="B15" t="n">
         <v>92321</v>
@@ -2233,19 +2229,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687515</v>
+        <v>687553</v>
       </c>
       <c r="R15" t="n">
-        <v>7096129</v>
+        <v>7096117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,7 +2289,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2315,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332772</v>
+        <v>124332779</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,21 +2323,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2362,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687611</v>
+        <v>687626</v>
       </c>
       <c r="R16" t="n">
-        <v>7096125</v>
+        <v>7096139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2435,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332732</v>
+        <v>124332730</v>
       </c>
       <c r="B17" t="n">
         <v>92285</v>
@@ -2479,10 +2471,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687561</v>
+        <v>687548</v>
       </c>
       <c r="R17" t="n">
-        <v>7096151</v>
+        <v>7096159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2551,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332758</v>
+        <v>124332747</v>
       </c>
       <c r="B18" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,21 +2559,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2595,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R18" t="n">
-        <v>7096128</v>
+        <v>7096156</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2641,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2668,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332771</v>
+        <v>124332769</v>
       </c>
       <c r="B19" t="n">
         <v>92321</v>
@@ -2715,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687471</v>
+        <v>687515</v>
       </c>
       <c r="R19" t="n">
-        <v>7096139</v>
+        <v>7096129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2788,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332787</v>
+        <v>124332758</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,21 +2795,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2826,19 +2817,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687548</v>
+        <v>687553</v>
       </c>
       <c r="R20" t="n">
-        <v>7096130</v>
+        <v>7096128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2908,7 +2896,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332731</v>
+        <v>124332776</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2946,16 +2934,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687535</v>
+        <v>687475</v>
       </c>
       <c r="R21" t="n">
-        <v>7096147</v>
+        <v>7096137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3006,6 +2997,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3024,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332745</v>
+        <v>124332772</v>
       </c>
       <c r="B22" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3040,21 +3032,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3062,16 +3054,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687633</v>
+        <v>687611</v>
       </c>
       <c r="R22" t="n">
-        <v>7096189</v>
+        <v>7096125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3122,6 +3117,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332760</v>
+        <v>124332771</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,25 +3148,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3178,16 +3174,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687631</v>
+        <v>687471</v>
       </c>
       <c r="R23" t="n">
-        <v>7096155</v>
+        <v>7096139</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332735</v>
+        <v>124332760</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,25 +3268,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687625</v>
+        <v>687631</v>
       </c>
       <c r="R24" t="n">
-        <v>7096144</v>
+        <v>7096155</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -2427,10 +2427,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332730</v>
+        <v>124332769</v>
       </c>
       <c r="B17" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2465,16 +2465,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687548</v>
+        <v>687515</v>
       </c>
       <c r="R17" t="n">
-        <v>7096159</v>
+        <v>7096129</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,6 +2528,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2543,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332747</v>
+        <v>124332730</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2587,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687633</v>
+        <v>687548</v>
       </c>
       <c r="R18" t="n">
-        <v>7096156</v>
+        <v>7096159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,7 +2663,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332769</v>
+        <v>124332747</v>
       </c>
       <c r="B19" t="n">
         <v>92321</v>
@@ -2697,19 +2701,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687515</v>
+        <v>687633</v>
       </c>
       <c r="R19" t="n">
-        <v>7096129</v>
+        <v>7096156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2760,7 +2761,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332742</v>
+        <v>124332779</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,16 +825,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687577</v>
+        <v>687626</v>
       </c>
       <c r="R3" t="n">
-        <v>7096121</v>
+        <v>7096139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332782</v>
+        <v>124332740</v>
       </c>
       <c r="B4" t="n">
-        <v>90051</v>
+        <v>92285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,19 +945,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687628</v>
+        <v>687507</v>
       </c>
       <c r="R4" t="n">
-        <v>7096143</v>
+        <v>7096131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332738</v>
+        <v>124332731</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687514</v>
+        <v>687535</v>
       </c>
       <c r="R5" t="n">
-        <v>7096131</v>
+        <v>7096147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332745</v>
+        <v>124332771</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,16 +1177,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687633</v>
+        <v>687471</v>
       </c>
       <c r="R6" t="n">
-        <v>7096189</v>
+        <v>7096139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,6 +1240,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332744</v>
+        <v>124332745</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1371,7 +1375,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332735</v>
+        <v>124332787</v>
       </c>
       <c r="B8" t="n">
         <v>92321</v>
@@ -1409,16 +1413,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687625</v>
+        <v>687548</v>
       </c>
       <c r="R8" t="n">
-        <v>7096144</v>
+        <v>7096130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,6 +1476,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332780</v>
+        <v>124332732</v>
       </c>
       <c r="B9" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1511,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,19 +1533,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687681</v>
+        <v>687561</v>
       </c>
       <c r="R9" t="n">
-        <v>7096188</v>
+        <v>7096151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1593,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332731</v>
+        <v>124332747</v>
       </c>
       <c r="B10" t="n">
         <v>92321</v>
@@ -1651,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687535</v>
+        <v>687633</v>
       </c>
       <c r="R10" t="n">
-        <v>7096147</v>
+        <v>7096156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332787</v>
+        <v>124332738</v>
       </c>
       <c r="B11" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1761,19 +1765,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687548</v>
+        <v>687514</v>
       </c>
       <c r="R11" t="n">
-        <v>7096130</v>
+        <v>7096131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1825,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332732</v>
+        <v>124332769</v>
       </c>
       <c r="B12" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1881,16 +1881,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687561</v>
+        <v>687515</v>
       </c>
       <c r="R12" t="n">
-        <v>7096151</v>
+        <v>7096129</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,6 +1944,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332736</v>
+        <v>124332744</v>
       </c>
       <c r="B13" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1979,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2003,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687498</v>
+        <v>687633</v>
       </c>
       <c r="R13" t="n">
-        <v>7096136</v>
+        <v>7096189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2075,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332740</v>
+        <v>124332776</v>
       </c>
       <c r="B14" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2113,16 +2117,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687507</v>
+        <v>687475</v>
       </c>
       <c r="R14" t="n">
-        <v>7096131</v>
+        <v>7096137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2173,6 +2180,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332737</v>
+        <v>124332758</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,21 +2215,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2238,7 +2246,7 @@
         <v>687553</v>
       </c>
       <c r="R15" t="n">
-        <v>7096117</v>
+        <v>7096128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,6 +2297,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2307,10 +2316,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332779</v>
+        <v>124332742</v>
       </c>
       <c r="B16" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2345,19 +2354,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687626</v>
+        <v>687577</v>
       </c>
       <c r="R16" t="n">
-        <v>7096139</v>
+        <v>7096121</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2408,7 +2414,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332769</v>
+        <v>124332730</v>
       </c>
       <c r="B17" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,21 +2448,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2465,19 +2470,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687515</v>
+        <v>687548</v>
       </c>
       <c r="R17" t="n">
-        <v>7096129</v>
+        <v>7096159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2530,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2547,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332730</v>
+        <v>124332736</v>
       </c>
       <c r="B18" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2564,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2591,10 +2592,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687548</v>
+        <v>687498</v>
       </c>
       <c r="R18" t="n">
-        <v>7096159</v>
+        <v>7096136</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332747</v>
+        <v>124332782</v>
       </c>
       <c r="B19" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,21 +2680,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2701,16 +2702,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687633</v>
+        <v>687628</v>
       </c>
       <c r="R19" t="n">
-        <v>7096156</v>
+        <v>7096143</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,6 +2765,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2779,7 +2784,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332758</v>
+        <v>124332780</v>
       </c>
       <c r="B20" t="n">
         <v>92309</v>
@@ -2817,16 +2822,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687553</v>
+        <v>687681</v>
       </c>
       <c r="R20" t="n">
-        <v>7096128</v>
+        <v>7096188</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2896,7 +2904,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332776</v>
+        <v>124332772</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2943,10 +2951,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687475</v>
+        <v>687611</v>
       </c>
       <c r="R21" t="n">
-        <v>7096137</v>
+        <v>7096125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,10 +3024,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332772</v>
+        <v>124332760</v>
       </c>
       <c r="B22" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,25 +3036,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3054,19 +3062,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687611</v>
+        <v>687631</v>
       </c>
       <c r="R22" t="n">
-        <v>7096125</v>
+        <v>7096155</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,7 +3122,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3136,7 +3140,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332771</v>
+        <v>124332737</v>
       </c>
       <c r="B23" t="n">
         <v>92321</v>
@@ -3174,19 +3178,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687471</v>
+        <v>687553</v>
       </c>
       <c r="R23" t="n">
-        <v>7096139</v>
+        <v>7096117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3237,7 +3238,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332760</v>
+        <v>124332735</v>
       </c>
       <c r="B24" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,25 +3268,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687631</v>
+        <v>687625</v>
       </c>
       <c r="R24" t="n">
-        <v>7096155</v>
+        <v>7096144</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332779</v>
+        <v>124332730</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,19 +825,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687626</v>
+        <v>687548</v>
       </c>
       <c r="R3" t="n">
-        <v>7096139</v>
+        <v>7096159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332740</v>
+        <v>124332742</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687507</v>
+        <v>687577</v>
       </c>
       <c r="R4" t="n">
-        <v>7096131</v>
+        <v>7096121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332731</v>
+        <v>124332744</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687535</v>
+        <v>687633</v>
       </c>
       <c r="R5" t="n">
-        <v>7096147</v>
+        <v>7096189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332771</v>
+        <v>124332760</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,19 +1173,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687471</v>
+        <v>687631</v>
       </c>
       <c r="R6" t="n">
-        <v>7096139</v>
+        <v>7096155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1233,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332745</v>
+        <v>124332769</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1297,16 +1289,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687633</v>
+        <v>687515</v>
       </c>
       <c r="R7" t="n">
-        <v>7096189</v>
+        <v>7096129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,6 +1352,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332787</v>
+        <v>124332737</v>
       </c>
       <c r="B8" t="n">
         <v>92321</v>
@@ -1413,19 +1409,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687548</v>
+        <v>687553</v>
       </c>
       <c r="R8" t="n">
-        <v>7096130</v>
+        <v>7096117</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1469,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1495,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332732</v>
+        <v>124332782</v>
       </c>
       <c r="B9" t="n">
-        <v>92285</v>
+        <v>90051</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1533,16 +1525,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687561</v>
+        <v>687628</v>
       </c>
       <c r="R9" t="n">
-        <v>7096151</v>
+        <v>7096143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,6 +1588,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332747</v>
+        <v>124332740</v>
       </c>
       <c r="B10" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1655,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687633</v>
+        <v>687507</v>
       </c>
       <c r="R10" t="n">
-        <v>7096156</v>
+        <v>7096131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332738</v>
+        <v>124332776</v>
       </c>
       <c r="B11" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1739,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1765,16 +1761,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687514</v>
+        <v>687475</v>
       </c>
       <c r="R11" t="n">
-        <v>7096131</v>
+        <v>7096137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,6 +1824,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332769</v>
+        <v>124332736</v>
       </c>
       <c r="B12" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1881,19 +1881,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687515</v>
+        <v>687498</v>
       </c>
       <c r="R12" t="n">
-        <v>7096129</v>
+        <v>7096136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1963,7 +1959,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332744</v>
+        <v>124332738</v>
       </c>
       <c r="B13" t="n">
         <v>92285</v>
@@ -2007,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687633</v>
+        <v>687514</v>
       </c>
       <c r="R13" t="n">
-        <v>7096189</v>
+        <v>7096131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332776</v>
+        <v>124332780</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687475</v>
+        <v>687681</v>
       </c>
       <c r="R14" t="n">
-        <v>7096137</v>
+        <v>7096188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332758</v>
+        <v>124332732</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2243,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687553</v>
+        <v>687561</v>
       </c>
       <c r="R15" t="n">
-        <v>7096128</v>
+        <v>7096151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2293,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2316,7 +2311,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332742</v>
+        <v>124332772</v>
       </c>
       <c r="B16" t="n">
         <v>92321</v>
@@ -2354,16 +2349,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687577</v>
+        <v>687611</v>
       </c>
       <c r="R16" t="n">
-        <v>7096121</v>
+        <v>7096125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,6 +2412,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2432,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332730</v>
+        <v>124332787</v>
       </c>
       <c r="B17" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,21 +2447,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2470,6 +2469,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
@@ -2479,7 +2481,7 @@
         <v>687548</v>
       </c>
       <c r="R17" t="n">
-        <v>7096159</v>
+        <v>7096130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,6 +2532,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2548,7 +2551,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332736</v>
+        <v>124332758</v>
       </c>
       <c r="B18" t="n">
         <v>92309</v>
@@ -2592,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687498</v>
+        <v>687553</v>
       </c>
       <c r="R18" t="n">
-        <v>7096136</v>
+        <v>7096128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2646,6 +2649,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2664,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332782</v>
+        <v>124332735</v>
       </c>
       <c r="B19" t="n">
-        <v>90051</v>
+        <v>92321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2702,19 +2706,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687628</v>
+        <v>687625</v>
       </c>
       <c r="R19" t="n">
-        <v>7096143</v>
+        <v>7096144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2766,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332780</v>
+        <v>124332731</v>
       </c>
       <c r="B20" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2822,19 +2822,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687681</v>
+        <v>687535</v>
       </c>
       <c r="R20" t="n">
-        <v>7096188</v>
+        <v>7096147</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,7 +2882,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2904,7 +2900,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332772</v>
+        <v>124332771</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2951,10 +2947,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687611</v>
+        <v>687471</v>
       </c>
       <c r="R21" t="n">
-        <v>7096125</v>
+        <v>7096139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3024,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332760</v>
+        <v>124332745</v>
       </c>
       <c r="B22" t="n">
-        <v>92293</v>
+        <v>92287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,25 +3032,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3068,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687631</v>
+        <v>687633</v>
       </c>
       <c r="R22" t="n">
-        <v>7096155</v>
+        <v>7096189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3140,7 +3136,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332737</v>
+        <v>124332747</v>
       </c>
       <c r="B23" t="n">
         <v>92321</v>
@@ -3184,10 +3180,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687553</v>
+        <v>687633</v>
       </c>
       <c r="R23" t="n">
-        <v>7096117</v>
+        <v>7096156</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332735</v>
+        <v>124332779</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3294,16 +3290,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687625</v>
+        <v>687626</v>
       </c>
       <c r="R24" t="n">
-        <v>7096144</v>
+        <v>7096139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3354,6 +3353,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332730</v>
+        <v>124332771</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,16 +825,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687548</v>
+        <v>687471</v>
       </c>
       <c r="R3" t="n">
-        <v>7096159</v>
+        <v>7096139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332742</v>
+        <v>124332779</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,16 +945,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687577</v>
+        <v>687626</v>
       </c>
       <c r="R4" t="n">
-        <v>7096121</v>
+        <v>7096139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +1008,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332744</v>
+        <v>124332782</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>90051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,16 +1065,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687633</v>
+        <v>687628</v>
       </c>
       <c r="R5" t="n">
-        <v>7096189</v>
+        <v>7096143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,6 +1128,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332760</v>
+        <v>124332742</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687631</v>
+        <v>687577</v>
       </c>
       <c r="R6" t="n">
-        <v>7096155</v>
+        <v>7096121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,17 +1256,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332769</v>
+        <v>124332744</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1289,19 +1301,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687515</v>
+        <v>687633</v>
       </c>
       <c r="R7" t="n">
-        <v>7096129</v>
+        <v>7096189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1361,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,14 +1372,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332737</v>
+        <v>124332787</v>
       </c>
       <c r="B8" t="n">
         <v>92321</v>
@@ -1409,16 +1417,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687553</v>
+        <v>687548</v>
       </c>
       <c r="R8" t="n">
-        <v>7096117</v>
+        <v>7096130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,6 +1480,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332782</v>
+        <v>124332731</v>
       </c>
       <c r="B9" t="n">
-        <v>90051</v>
+        <v>92321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1515,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,19 +1537,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687628</v>
+        <v>687535</v>
       </c>
       <c r="R9" t="n">
-        <v>7096143</v>
+        <v>7096147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1597,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1600,14 +1608,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332740</v>
+        <v>124332732</v>
       </c>
       <c r="B10" t="n">
         <v>92285</v>
@@ -1651,10 +1659,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687507</v>
+        <v>687561</v>
       </c>
       <c r="R10" t="n">
-        <v>7096131</v>
+        <v>7096151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,14 +1724,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332776</v>
+        <v>124332737</v>
       </c>
       <c r="B11" t="n">
         <v>92321</v>
@@ -1761,19 +1769,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687475</v>
+        <v>687553</v>
       </c>
       <c r="R11" t="n">
-        <v>7096137</v>
+        <v>7096117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1829,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1836,17 +1840,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332736</v>
+        <v>124332738</v>
       </c>
       <c r="B12" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,21 +1863,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1887,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687498</v>
+        <v>687514</v>
       </c>
       <c r="R12" t="n">
-        <v>7096136</v>
+        <v>7096131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,14 +1956,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332738</v>
+        <v>124332730</v>
       </c>
       <c r="B13" t="n">
         <v>92285</v>
@@ -2003,10 +2007,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687514</v>
+        <v>687548</v>
       </c>
       <c r="R13" t="n">
-        <v>7096131</v>
+        <v>7096159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,17 +2072,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332780</v>
+        <v>124332747</v>
       </c>
       <c r="B14" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2113,19 +2117,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687681</v>
+        <v>687633</v>
       </c>
       <c r="R14" t="n">
-        <v>7096188</v>
+        <v>7096156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2177,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2188,17 +2188,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332732</v>
+        <v>124332736</v>
       </c>
       <c r="B15" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687561</v>
+        <v>687498</v>
       </c>
       <c r="R15" t="n">
-        <v>7096151</v>
+        <v>7096136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,17 +2304,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332772</v>
+        <v>124332760</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,25 +2323,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2349,19 +2349,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687611</v>
+        <v>687631</v>
       </c>
       <c r="R16" t="n">
-        <v>7096125</v>
+        <v>7096155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,7 +2409,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2431,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332787</v>
+        <v>124332772</v>
       </c>
       <c r="B17" t="n">
         <v>92321</v>
@@ -2478,10 +2474,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687548</v>
+        <v>687611</v>
       </c>
       <c r="R17" t="n">
-        <v>7096130</v>
+        <v>7096125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2551,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332758</v>
+        <v>124332735</v>
       </c>
       <c r="B18" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2595,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687553</v>
+        <v>687625</v>
       </c>
       <c r="R18" t="n">
-        <v>7096128</v>
+        <v>7096144</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2645,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2661,17 +2656,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332735</v>
+        <v>124332758</v>
       </c>
       <c r="B19" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,21 +2679,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2712,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687625</v>
+        <v>687553</v>
       </c>
       <c r="R19" t="n">
-        <v>7096144</v>
+        <v>7096128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,6 +2761,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2784,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332731</v>
+        <v>124332745</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2828,10 +2824,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687535</v>
+        <v>687633</v>
       </c>
       <c r="R20" t="n">
-        <v>7096147</v>
+        <v>7096189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2893,14 +2889,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332771</v>
+        <v>124332776</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2947,10 +2943,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687471</v>
+        <v>687475</v>
       </c>
       <c r="R21" t="n">
-        <v>7096139</v>
+        <v>7096137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3020,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332745</v>
+        <v>124332740</v>
       </c>
       <c r="B22" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,21 +3032,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3064,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687633</v>
+        <v>687507</v>
       </c>
       <c r="R22" t="n">
-        <v>7096189</v>
+        <v>7096131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3129,14 +3125,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Ulf Hallin, Lukas Holmström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332747</v>
+        <v>124332769</v>
       </c>
       <c r="B23" t="n">
         <v>92321</v>
@@ -3174,16 +3170,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687633</v>
+        <v>687515</v>
       </c>
       <c r="R23" t="n">
-        <v>7096156</v>
+        <v>7096129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3234,6 +3233,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332779</v>
+        <v>124332780</v>
       </c>
       <c r="B24" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687626</v>
+        <v>687681</v>
       </c>
       <c r="R24" t="n">
-        <v>7096139</v>
+        <v>7096188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332771</v>
+        <v>124332730</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,19 +825,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687471</v>
+        <v>687548</v>
       </c>
       <c r="R3" t="n">
-        <v>7096139</v>
+        <v>7096159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332779</v>
+        <v>124332747</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,19 +941,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687626</v>
+        <v>687633</v>
       </c>
       <c r="R4" t="n">
-        <v>7096139</v>
+        <v>7096156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332782</v>
+        <v>124332758</v>
       </c>
       <c r="B5" t="n">
-        <v>90051</v>
+        <v>92309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,19 +1057,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687628</v>
+        <v>687553</v>
       </c>
       <c r="R5" t="n">
-        <v>7096143</v>
+        <v>7096128</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332742</v>
+        <v>124332776</v>
       </c>
       <c r="B6" t="n">
         <v>92321</v>
@@ -1185,16 +1174,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687577</v>
+        <v>687475</v>
       </c>
       <c r="R6" t="n">
-        <v>7096121</v>
+        <v>7096137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,6 +1237,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,17 +1249,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332744</v>
+        <v>124332745</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,21 +1272,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1372,7 +1365,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1499,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332731</v>
+        <v>124332782</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>90051</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1537,16 +1530,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687535</v>
+        <v>687628</v>
       </c>
       <c r="R9" t="n">
-        <v>7096147</v>
+        <v>7096143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,6 +1593,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1608,17 +1605,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332732</v>
+        <v>124332736</v>
       </c>
       <c r="B10" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1659,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687561</v>
+        <v>687498</v>
       </c>
       <c r="R10" t="n">
-        <v>7096151</v>
+        <v>7096136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,17 +1721,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332737</v>
+        <v>124332779</v>
       </c>
       <c r="B11" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,16 +1766,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687553</v>
+        <v>687626</v>
       </c>
       <c r="R11" t="n">
-        <v>7096117</v>
+        <v>7096139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,6 +1829,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1840,17 +1841,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332738</v>
+        <v>124332780</v>
       </c>
       <c r="B12" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,21 +1864,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1885,16 +1886,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687514</v>
+        <v>687681</v>
       </c>
       <c r="R12" t="n">
-        <v>7096131</v>
+        <v>7096188</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,6 +1949,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1956,17 +1961,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332730</v>
+        <v>124332731</v>
       </c>
       <c r="B13" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,21 +1984,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687548</v>
+        <v>687535</v>
       </c>
       <c r="R13" t="n">
-        <v>7096159</v>
+        <v>7096147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2072,17 +2077,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332747</v>
+        <v>124332732</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2100,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687633</v>
+        <v>687561</v>
       </c>
       <c r="R14" t="n">
-        <v>7096156</v>
+        <v>7096151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,17 +2193,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332736</v>
+        <v>124332738</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2216,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2239,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687498</v>
+        <v>687514</v>
       </c>
       <c r="R15" t="n">
-        <v>7096136</v>
+        <v>7096131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,17 +2309,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332760</v>
+        <v>124332740</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>92285</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,25 +2328,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2355,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687631</v>
+        <v>687507</v>
       </c>
       <c r="R16" t="n">
-        <v>7096155</v>
+        <v>7096131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332772</v>
+        <v>124332737</v>
       </c>
       <c r="B17" t="n">
         <v>92321</v>
@@ -2465,19 +2470,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687611</v>
+        <v>687553</v>
       </c>
       <c r="R17" t="n">
-        <v>7096125</v>
+        <v>7096117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2530,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2656,17 +2657,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332758</v>
+        <v>124332771</v>
       </c>
       <c r="B19" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,21 +2680,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2701,16 +2702,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687553</v>
+        <v>687471</v>
       </c>
       <c r="R19" t="n">
-        <v>7096128</v>
+        <v>7096139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2780,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332745</v>
+        <v>124332772</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2818,16 +2822,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687633</v>
+        <v>687611</v>
       </c>
       <c r="R20" t="n">
-        <v>7096189</v>
+        <v>7096125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,6 +2885,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2889,14 +2897,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332776</v>
+        <v>124332742</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2934,19 +2942,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687475</v>
+        <v>687577</v>
       </c>
       <c r="R21" t="n">
-        <v>7096137</v>
+        <v>7096121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,7 +3002,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3016,7 +3020,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332740</v>
+        <v>124332744</v>
       </c>
       <c r="B22" t="n">
         <v>92285</v>
@@ -3060,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687507</v>
+        <v>687633</v>
       </c>
       <c r="R22" t="n">
-        <v>7096131</v>
+        <v>7096189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,17 +3129,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Lukas Holmström</t>
+          <t>Lukas Holmström, Ulf Hallin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332769</v>
+        <v>124332760</v>
       </c>
       <c r="B23" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3144,25 +3148,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3170,19 +3174,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687515</v>
+        <v>687631</v>
       </c>
       <c r="R23" t="n">
-        <v>7096129</v>
+        <v>7096155</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,7 +3234,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332780</v>
+        <v>124332769</v>
       </c>
       <c r="B24" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687681</v>
+        <v>687515</v>
       </c>
       <c r="R24" t="n">
-        <v>7096188</v>
+        <v>7096129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -2316,10 +2316,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332740</v>
+        <v>124332737</v>
       </c>
       <c r="B16" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687507</v>
+        <v>687553</v>
       </c>
       <c r="R16" t="n">
-        <v>7096131</v>
+        <v>7096117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332737</v>
+        <v>124332740</v>
       </c>
       <c r="B17" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687553</v>
+        <v>687507</v>
       </c>
       <c r="R17" t="n">
-        <v>7096117</v>
+        <v>7096131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332747</v>
+        <v>124332787</v>
       </c>
       <c r="B4" t="n">
         <v>92321</v>
@@ -941,16 +941,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687633</v>
+        <v>687548</v>
       </c>
       <c r="R4" t="n">
-        <v>7096156</v>
+        <v>7096130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332758</v>
+        <v>124332771</v>
       </c>
       <c r="B5" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,16 +1061,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687553</v>
+        <v>687471</v>
       </c>
       <c r="R5" t="n">
-        <v>7096128</v>
+        <v>7096139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332776</v>
+        <v>124332745</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,19 +1181,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687475</v>
+        <v>687633</v>
       </c>
       <c r="R6" t="n">
-        <v>7096137</v>
+        <v>7096189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1241,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332745</v>
+        <v>124332769</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1294,16 +1297,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687633</v>
+        <v>687515</v>
       </c>
       <c r="R7" t="n">
-        <v>7096189</v>
+        <v>7096129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,6 +1360,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332787</v>
+        <v>124332736</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1395,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1410,19 +1417,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687548</v>
+        <v>687498</v>
       </c>
       <c r="R8" t="n">
-        <v>7096130</v>
+        <v>7096136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1477,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1492,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332782</v>
+        <v>124332737</v>
       </c>
       <c r="B9" t="n">
-        <v>90051</v>
+        <v>92321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,21 +1511,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1530,19 +1533,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687628</v>
+        <v>687553</v>
       </c>
       <c r="R9" t="n">
-        <v>7096143</v>
+        <v>7096117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1612,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332736</v>
+        <v>124332735</v>
       </c>
       <c r="B10" t="n">
-        <v>92309</v>
+        <v>92321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1656,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687498</v>
+        <v>687625</v>
       </c>
       <c r="R10" t="n">
-        <v>7096136</v>
+        <v>7096144</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332779</v>
+        <v>124332782</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>90051</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1775,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687626</v>
+        <v>687628</v>
       </c>
       <c r="R11" t="n">
-        <v>7096139</v>
+        <v>7096143</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124332780</v>
+        <v>124332744</v>
       </c>
       <c r="B12" t="n">
-        <v>92309</v>
+        <v>92285</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,21 +1863,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1886,19 +1885,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687681</v>
+        <v>687633</v>
       </c>
       <c r="R12" t="n">
-        <v>7096188</v>
+        <v>7096189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,7 +1945,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332731</v>
+        <v>124332772</v>
       </c>
       <c r="B13" t="n">
         <v>92321</v>
@@ -2006,16 +2001,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687535</v>
+        <v>687611</v>
       </c>
       <c r="R13" t="n">
-        <v>7096147</v>
+        <v>7096125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,6 +2064,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2084,7 +2083,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332732</v>
+        <v>124332738</v>
       </c>
       <c r="B14" t="n">
         <v>92285</v>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687561</v>
+        <v>687514</v>
       </c>
       <c r="R14" t="n">
-        <v>7096151</v>
+        <v>7096131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2200,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332738</v>
+        <v>124332776</v>
       </c>
       <c r="B15" t="n">
-        <v>92285</v>
+        <v>92321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,21 +2215,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2238,16 +2237,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687514</v>
+        <v>687475</v>
       </c>
       <c r="R15" t="n">
-        <v>7096131</v>
+        <v>7096137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,6 +2300,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2316,7 +2319,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332737</v>
+        <v>124332731</v>
       </c>
       <c r="B16" t="n">
         <v>92321</v>
@@ -2360,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687553</v>
+        <v>687535</v>
       </c>
       <c r="R16" t="n">
-        <v>7096117</v>
+        <v>7096147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332740</v>
+        <v>124332758</v>
       </c>
       <c r="B17" t="n">
-        <v>92285</v>
+        <v>92309</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,21 +2451,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2476,10 +2479,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687507</v>
+        <v>687553</v>
       </c>
       <c r="R17" t="n">
-        <v>7096131</v>
+        <v>7096128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,6 +2533,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2548,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124332735</v>
+        <v>124332760</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2560,25 +2564,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2592,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687625</v>
+        <v>687631</v>
       </c>
       <c r="R18" t="n">
-        <v>7096144</v>
+        <v>7096155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332771</v>
+        <v>124332740</v>
       </c>
       <c r="B19" t="n">
-        <v>92321</v>
+        <v>92285</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2702,19 +2706,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687471</v>
+        <v>687507</v>
       </c>
       <c r="R19" t="n">
-        <v>7096139</v>
+        <v>7096131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2766,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332772</v>
+        <v>124332780</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>92309</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687611</v>
+        <v>687681</v>
       </c>
       <c r="R20" t="n">
-        <v>7096125</v>
+        <v>7096188</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332742</v>
+        <v>124332747</v>
       </c>
       <c r="B21" t="n">
         <v>92321</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687577</v>
+        <v>687633</v>
       </c>
       <c r="R21" t="n">
-        <v>7096121</v>
+        <v>7096156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332744</v>
+        <v>124332732</v>
       </c>
       <c r="B22" t="n">
         <v>92285</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687633</v>
+        <v>687561</v>
       </c>
       <c r="R22" t="n">
-        <v>7096189</v>
+        <v>7096151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332760</v>
+        <v>124332742</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,25 +3148,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687631</v>
+        <v>687577</v>
       </c>
       <c r="R23" t="n">
-        <v>7096155</v>
+        <v>7096121</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332769</v>
+        <v>124332779</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>92287</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687515</v>
+        <v>687626</v>
       </c>
       <c r="R24" t="n">
-        <v>7096129</v>
+        <v>7096139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3370,6 +3370,2170 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128423054</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>687469</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7096069</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128423068</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687431</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7096053</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128423063</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>687549</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7095972</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128423061</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>687573</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7095996</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128423065</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>687544</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7095975</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128423057</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>687752</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7096003</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128423069</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>687381</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7096073</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128423059</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>687601</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7096029</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128423056</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>687770</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7095995</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128423058</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687655</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7096022</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128423062</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>687564</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7095983</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128397375</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687623</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7096044</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128423049</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687529</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7096012</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128423067</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>687520</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7096043</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128423064</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>687549</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7095982</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128423053</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>687504</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7096055</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128423050</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>687474</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7096071</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128397032</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>687574</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7096060</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128423055</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>687441</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7096052</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128423052</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>687531</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7096010</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128397014</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>687582</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7096036</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128423066</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Einarstjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>687511</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7096024</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3472,7 +3472,7 @@
         <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423057</v>
+        <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687752</v>
+        <v>687381</v>
       </c>
       <c r="R30" t="n">
-        <v>7096003</v>
+        <v>7096073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,39 +3947,39 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423069</v>
+        <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>92648</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687381</v>
+        <v>687601</v>
       </c>
       <c r="R31" t="n">
-        <v>7096073</v>
+        <v>7096029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B32" t="n">
         <v>79032</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R32" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423056</v>
+        <v>128423058</v>
       </c>
       <c r="B33" t="n">
         <v>79032</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687770</v>
+        <v>687655</v>
       </c>
       <c r="R33" t="n">
-        <v>7095995</v>
+        <v>7096022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423058</v>
+        <v>128423057</v>
       </c>
       <c r="B34" t="n">
         <v>79032</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687655</v>
+        <v>687752</v>
       </c>
       <c r="R34" t="n">
-        <v>7096022</v>
+        <v>7096003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,19 +5126,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B43" t="n">
         <v>79032</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5223,22 +5233,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5256,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5353,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5138,7 +5138,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128397014</v>
+        <v>128423055</v>
       </c>
       <c r="B43" t="n">
         <v>79032</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687582</v>
+        <v>687441</v>
       </c>
       <c r="R43" t="n">
-        <v>7096036</v>
+        <v>7096052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,22 +5223,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5256,21 +5246,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5280,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687531</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5342,10 +5332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423052</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,34 +5343,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687531</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096010</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128423056</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>128423058</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R41" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,19 +5002,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,34 +5042,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R42" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,12 +5126,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5141,7 +5141,7 @@
         <v>128423055</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R26" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R27" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423069</v>
+        <v>128423059</v>
       </c>
       <c r="B30" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687381</v>
+        <v>687601</v>
       </c>
       <c r="R30" t="n">
-        <v>7096073</v>
+        <v>7096029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B31" t="n">
         <v>79083</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R31" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423056</v>
+        <v>128423058</v>
       </c>
       <c r="B32" t="n">
         <v>79083</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687770</v>
+        <v>687655</v>
       </c>
       <c r="R32" t="n">
-        <v>7095995</v>
+        <v>7096022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423058</v>
+        <v>128423057</v>
       </c>
       <c r="B33" t="n">
         <v>79083</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687655</v>
+        <v>687752</v>
       </c>
       <c r="R33" t="n">
-        <v>7096022</v>
+        <v>7096003</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423057</v>
+        <v>128423069</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687752</v>
+        <v>687381</v>
       </c>
       <c r="R34" t="n">
-        <v>7096003</v>
+        <v>7096073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,12 +5126,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R41" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,19 +5002,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,34 +5042,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R42" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,19 +5126,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B43" t="n">
         <v>79083</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5223,22 +5233,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5256,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5353,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128423063</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128423068</v>
       </c>
       <c r="B27" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R28" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R29" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423059</v>
+        <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687601</v>
+        <v>687381</v>
       </c>
       <c r="R30" t="n">
-        <v>7096029</v>
+        <v>7096073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423056</v>
+        <v>128423057</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687770</v>
+        <v>687752</v>
       </c>
       <c r="R31" t="n">
-        <v>7095995</v>
+        <v>7096003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,7 +4054,7 @@
         <v>128423058</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423057</v>
+        <v>128423059</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687752</v>
+        <v>687601</v>
       </c>
       <c r="R33" t="n">
-        <v>7096003</v>
+        <v>7096029</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423069</v>
+        <v>128423056</v>
       </c>
       <c r="B34" t="n">
-        <v>92742</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687381</v>
+        <v>687770</v>
       </c>
       <c r="R34" t="n">
-        <v>7096073</v>
+        <v>7095995</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128397014</v>
+        <v>128423055</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687582</v>
+        <v>687441</v>
       </c>
       <c r="R43" t="n">
-        <v>7096036</v>
+        <v>7096052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,22 +5223,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5256,21 +5246,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5280,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687531</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5342,10 +5332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423052</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,34 +5343,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687531</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096010</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>92754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R26" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R27" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B26" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R26" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R27" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R28" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R29" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
         <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423057</v>
+        <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687752</v>
+        <v>687601</v>
       </c>
       <c r="R31" t="n">
-        <v>7096003</v>
+        <v>7096029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423058</v>
+        <v>128423056</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687655</v>
+        <v>687770</v>
       </c>
       <c r="R32" t="n">
-        <v>7096022</v>
+        <v>7095995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423059</v>
+        <v>128423058</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687601</v>
+        <v>687655</v>
       </c>
       <c r="R33" t="n">
-        <v>7096029</v>
+        <v>7096022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423056</v>
+        <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687770</v>
+        <v>687752</v>
       </c>
       <c r="R34" t="n">
-        <v>7095995</v>
+        <v>7096003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5223,22 +5233,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5256,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5353,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R26" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R27" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,14 +3656,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B28" t="n">
         <v>79089</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R28" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B29" t="n">
         <v>79089</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R29" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423059</v>
+        <v>128423057</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687601</v>
+        <v>687752</v>
       </c>
       <c r="R31" t="n">
-        <v>7096029</v>
+        <v>7096003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423056</v>
+        <v>128423058</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687770</v>
+        <v>687655</v>
       </c>
       <c r="R32" t="n">
-        <v>7095995</v>
+        <v>7096022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423058</v>
+        <v>128423059</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687655</v>
+        <v>687601</v>
       </c>
       <c r="R33" t="n">
-        <v>7096022</v>
+        <v>7096029</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423057</v>
+        <v>128423056</v>
       </c>
       <c r="B34" t="n">
         <v>79089</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687752</v>
+        <v>687770</v>
       </c>
       <c r="R34" t="n">
-        <v>7096003</v>
+        <v>7095995</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128397014</v>
+        <v>128423055</v>
       </c>
       <c r="B43" t="n">
         <v>79089</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687582</v>
+        <v>687441</v>
       </c>
       <c r="R43" t="n">
-        <v>7096036</v>
+        <v>7096052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,22 +5223,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5256,21 +5246,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5280,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687531</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5342,10 +5332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423052</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,34 +5343,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687531</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096010</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5138,7 +5138,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B43" t="n">
         <v>79089</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5223,22 +5233,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5256,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5353,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B26" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R26" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R27" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423069</v>
+        <v>128423057</v>
       </c>
       <c r="B30" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687381</v>
+        <v>687752</v>
       </c>
       <c r="R30" t="n">
-        <v>7096073</v>
+        <v>7096003</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423057</v>
+        <v>128423058</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687752</v>
+        <v>687655</v>
       </c>
       <c r="R31" t="n">
-        <v>7096003</v>
+        <v>7096022</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423058</v>
+        <v>128423059</v>
       </c>
       <c r="B32" t="n">
         <v>79089</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687655</v>
+        <v>687601</v>
       </c>
       <c r="R32" t="n">
-        <v>7096022</v>
+        <v>7096029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R33" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423056</v>
+        <v>128423069</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687770</v>
+        <v>687381</v>
       </c>
       <c r="R34" t="n">
-        <v>7095995</v>
+        <v>7096073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R41" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,19 +5002,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,34 +5042,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R42" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5149,34 +5149,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R43" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,12 +5223,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5342,10 +5332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423052</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,34 +5343,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687531</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096010</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423063</v>
+        <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687549</v>
+        <v>687431</v>
       </c>
       <c r="R26" t="n">
-        <v>7095972</v>
+        <v>7096053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,39 +3559,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423068</v>
+        <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687431</v>
+        <v>687549</v>
       </c>
       <c r="R27" t="n">
-        <v>7096053</v>
+        <v>7095972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R28" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R29" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423057</v>
+        <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687752</v>
+        <v>687381</v>
       </c>
       <c r="R30" t="n">
-        <v>7096003</v>
+        <v>7096073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423058</v>
+        <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687655</v>
+        <v>687601</v>
       </c>
       <c r="R31" t="n">
-        <v>7096022</v>
+        <v>7096029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R32" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423056</v>
+        <v>128423058</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687770</v>
+        <v>687655</v>
       </c>
       <c r="R33" t="n">
-        <v>7095995</v>
+        <v>7096022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423069</v>
+        <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687381</v>
+        <v>687752</v>
       </c>
       <c r="R34" t="n">
-        <v>7096073</v>
+        <v>7096003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B43" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R43" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5246,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687531</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
         <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423069</v>
+        <v>128423059</v>
       </c>
       <c r="B30" t="n">
-        <v>92784</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687381</v>
+        <v>687601</v>
       </c>
       <c r="R30" t="n">
-        <v>7096073</v>
+        <v>7096029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B31" t="n">
         <v>79116</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R31" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423056</v>
+        <v>128423058</v>
       </c>
       <c r="B32" t="n">
         <v>79116</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687770</v>
+        <v>687655</v>
       </c>
       <c r="R32" t="n">
-        <v>7095995</v>
+        <v>7096022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423058</v>
+        <v>128423057</v>
       </c>
       <c r="B33" t="n">
         <v>79116</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687655</v>
+        <v>687752</v>
       </c>
       <c r="R33" t="n">
-        <v>7096022</v>
+        <v>7096003</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423057</v>
+        <v>128423069</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687752</v>
+        <v>687381</v>
       </c>
       <c r="R34" t="n">
-        <v>7096003</v>
+        <v>7096073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R41" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,19 +5002,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,34 +5042,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R42" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,19 +5126,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B43" t="n">
         <v>79116</v>
@@ -5169,14 +5169,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5223,22 +5233,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5256,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5353,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423059</v>
+        <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>92794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687601</v>
+        <v>687381</v>
       </c>
       <c r="R30" t="n">
-        <v>7096029</v>
+        <v>7096073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423056</v>
+        <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R31" t="n">
-        <v>7095995</v>
+        <v>7096029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423058</v>
+        <v>128423056</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687655</v>
+        <v>687770</v>
       </c>
       <c r="R32" t="n">
-        <v>7096022</v>
+        <v>7095995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423057</v>
+        <v>128423058</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687752</v>
+        <v>687655</v>
       </c>
       <c r="R33" t="n">
-        <v>7096003</v>
+        <v>7096022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423069</v>
+        <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>92784</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687381</v>
+        <v>687752</v>
       </c>
       <c r="R34" t="n">
-        <v>7096073</v>
+        <v>7096003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128397014</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>128423052</v>
       </c>
       <c r="B45" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3954,7 +3954,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423059</v>
+        <v>128423056</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R31" t="n">
-        <v>7096029</v>
+        <v>7095995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423056</v>
+        <v>128423059</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R32" t="n">
-        <v>7095995</v>
+        <v>7096029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,12 +5126,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5534,6 +5534,915 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128912701</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>687620</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7096086</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128912702</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>687654</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7096077</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128912698</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>687736</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7096043</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128912697</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>687805</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7095984</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128912704</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>687774</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7096150</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128912699</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>687675</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7096065</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128912700</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>687674</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7096063</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128912703</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>687712</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7096132</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128912705</v>
+      </c>
+      <c r="B55" t="n">
+        <v>81105</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>687769</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7096150</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79739</v>
+        <v>81105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81105</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3663,7 +3663,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R28" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B29" t="n">
         <v>79120</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R29" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423056</v>
+        <v>128423057</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687770</v>
+        <v>687752</v>
       </c>
       <c r="R31" t="n">
-        <v>7095995</v>
+        <v>7096003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423059</v>
+        <v>128423058</v>
       </c>
       <c r="B32" t="n">
         <v>79120</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687601</v>
+        <v>687655</v>
       </c>
       <c r="R32" t="n">
-        <v>7096029</v>
+        <v>7096022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423058</v>
+        <v>128423059</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687655</v>
+        <v>687601</v>
       </c>
       <c r="R33" t="n">
-        <v>7096022</v>
+        <v>7096029</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423057</v>
+        <v>128423056</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687752</v>
+        <v>687770</v>
       </c>
       <c r="R34" t="n">
-        <v>7096003</v>
+        <v>7095995</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R41" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,19 +5002,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,34 +5042,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R42" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5149,34 +5149,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R43" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5233,12 +5223,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5342,10 +5332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423052</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,34 +5343,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687531</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096010</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>81105</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
         <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>81109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423065</v>
+        <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687544</v>
+        <v>687573</v>
       </c>
       <c r="R28" t="n">
-        <v>7095975</v>
+        <v>7095996</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423061</v>
+        <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687573</v>
+        <v>687544</v>
       </c>
       <c r="R29" t="n">
-        <v>7095996</v>
+        <v>7095975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423069</v>
+        <v>128423059</v>
       </c>
       <c r="B30" t="n">
-        <v>92794</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687381</v>
+        <v>687601</v>
       </c>
       <c r="R30" t="n">
-        <v>7096073</v>
+        <v>7096029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423057</v>
+        <v>128423056</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687752</v>
+        <v>687770</v>
       </c>
       <c r="R31" t="n">
-        <v>7096003</v>
+        <v>7095995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,7 +4054,7 @@
         <v>128423058</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,32 +4148,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423059</v>
+        <v>128423069</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>92798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687601</v>
+        <v>687381</v>
       </c>
       <c r="R33" t="n">
-        <v>7096029</v>
+        <v>7096073</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,17 +4238,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423056</v>
+        <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687770</v>
+        <v>687752</v>
       </c>
       <c r="R34" t="n">
-        <v>7095995</v>
+        <v>7096003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>128423050</v>
       </c>
       <c r="B41" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128397032</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128423052</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,9 +5303,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5320,22 +5330,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423055</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5363,14 +5373,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687441</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5410,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>128912703</v>
       </c>
       <c r="B54" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687712</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096132</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -4934,10 +4934,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4945,34 +4945,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687574</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5002,9 +5002,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,34 +5052,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687474</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096071</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B43" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R43" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128397014</v>
+        <v>128423052</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,34 +5246,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687582</v>
+        <v>687531</v>
       </c>
       <c r="R44" t="n">
-        <v>7096036</v>
+        <v>7096010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,19 +5303,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5330,19 +5320,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128423055</v>
+        <v>128397014</v>
       </c>
       <c r="B45" t="n">
         <v>79124</v>
@@ -5373,14 +5363,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687441</v>
+        <v>687582</v>
       </c>
       <c r="R45" t="n">
-        <v>7096052</v>
+        <v>7096036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,9 +5400,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,12 +5427,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79743</v>
+        <v>81109</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B55" t="n">
-        <v>81109</v>
+        <v>79743</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -3375,7 +3375,7 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128423068</v>
       </c>
       <c r="B26" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128423063</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128423061</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128423065</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3857,32 +3857,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423059</v>
+        <v>128423069</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>92803</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687601</v>
+        <v>687381</v>
       </c>
       <c r="R30" t="n">
-        <v>7096029</v>
+        <v>7096073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423056</v>
+        <v>128423059</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R31" t="n">
-        <v>7095995</v>
+        <v>7096029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423058</v>
+        <v>128423056</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687655</v>
+        <v>687770</v>
       </c>
       <c r="R32" t="n">
-        <v>7096022</v>
+        <v>7095995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,32 +4148,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423069</v>
+        <v>128423058</v>
       </c>
       <c r="B33" t="n">
-        <v>92798</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687381</v>
+        <v>687655</v>
       </c>
       <c r="R33" t="n">
-        <v>7096073</v>
+        <v>7096022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
         <v>128423057</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128423062</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>128397375</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128423049</v>
       </c>
       <c r="B37" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128423067</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128423064</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128423053</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>128397032</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128423050</v>
       </c>
       <c r="B42" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128423055</v>
+        <v>128423052</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687441</v>
+        <v>687531</v>
       </c>
       <c r="R43" t="n">
-        <v>7096052</v>
+        <v>7096010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423052</v>
+        <v>128423055</v>
       </c>
       <c r="B44" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5246,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687531</v>
+        <v>687441</v>
       </c>
       <c r="R44" t="n">
-        <v>7096010</v>
+        <v>7096052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5335,7 +5335,7 @@
         <v>128397014</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>128423066</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>81109</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>81014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,7 +6347,7 @@
         <v>128912700</v>
       </c>
       <c r="B55" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>81019</v>
+        <v>79653</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>128912703</v>
       </c>
       <c r="B54" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687712</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096132</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>81019</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79653</v>
+        <v>81019</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81019</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>81019</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
         <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>81020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>81020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81020</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>81020</v>
+        <v>79654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B54" t="n">
-        <v>79654</v>
+        <v>81020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79654</v>
+        <v>81024</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>81020</v>
+        <v>79658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R54" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6347,7 +6347,7 @@
         <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>81024</v>
+        <v>79658</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>128912703</v>
       </c>
       <c r="B54" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687712</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096132</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>81024</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>81024</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B55" t="n">
-        <v>81024</v>
+        <v>79658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B54" t="n">
-        <v>81024</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R54" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79658</v>
+        <v>81026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79660</v>
+        <v>81026</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81026</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>81026</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>81026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B54" t="n">
-        <v>79660</v>
+        <v>81026</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912700</v>
       </c>
       <c r="B55" t="n">
-        <v>81026</v>
+        <v>79660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687674</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R53" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B54" t="n">
-        <v>81026</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R54" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>81026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912700</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79660</v>
+        <v>81028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687674</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096063</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912703</v>
+        <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687712</v>
+        <v>687674</v>
       </c>
       <c r="R54" t="n">
-        <v>7096132</v>
+        <v>7096063</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81026</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5539,7 +5539,7 @@
         <v>128912701</v>
       </c>
       <c r="B47" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>128912702</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>128912698</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>128912697</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128912699</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B53" t="n">
-        <v>81028</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6246,7 +6246,7 @@
         <v>128912700</v>
       </c>
       <c r="B54" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>81029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -5943,7 +5943,7 @@
         <v>128912704</v>
       </c>
       <c r="B51" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912703</v>
+        <v>128912705</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>81029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687712</v>
+        <v>687769</v>
       </c>
       <c r="R53" t="n">
-        <v>7096132</v>
+        <v>7096150</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912705</v>
+        <v>128912703</v>
       </c>
       <c r="B55" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687769</v>
+        <v>687712</v>
       </c>
       <c r="R55" t="n">
-        <v>7096150</v>
+        <v>7096132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61258291</v>
+        <v>17225811</v>
       </c>
       <c r="B2" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåbergsheden, Ång</t>
+          <t>Einarstjärnen SSO om Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687560.5063135701</v>
+        <v>687905</v>
       </c>
       <c r="R2" t="n">
-        <v>7096150.745734991</v>
+        <v>7096001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +756,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124332730</v>
+        <v>128912705</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,38 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687548</v>
+        <v>687769</v>
       </c>
       <c r="R3" t="n">
-        <v>7096159</v>
+        <v>7096150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,27 +874,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124332787</v>
+        <v>124332782</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687548</v>
+        <v>687628</v>
       </c>
       <c r="R4" t="n">
-        <v>7096130</v>
+        <v>7096143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,37 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124332771</v>
+        <v>124332736</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,19 +1038,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687471</v>
+        <v>687498</v>
       </c>
       <c r="R5" t="n">
-        <v>7096139</v>
+        <v>7096136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,37 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124332745</v>
+        <v>124332758</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1187,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687633</v>
+        <v>687553</v>
       </c>
       <c r="R6" t="n">
-        <v>7096189</v>
+        <v>7096128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,6 +1209,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,37 +1228,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124332769</v>
+        <v>124332780</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1306,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687515</v>
+        <v>687681</v>
       </c>
       <c r="R7" t="n">
-        <v>7096129</v>
+        <v>7096188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,15 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124332736</v>
+        <v>124332730</v>
       </c>
       <c r="B8" t="n">
-        <v>92309</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1423,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687498</v>
+        <v>687548</v>
       </c>
       <c r="R8" t="n">
-        <v>7096136</v>
+        <v>7096159</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,15 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124332737</v>
+        <v>124332732</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1539,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687553</v>
+        <v>687561</v>
       </c>
       <c r="R9" t="n">
-        <v>7096117</v>
+        <v>7096151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,15 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124332735</v>
+        <v>124332738</v>
       </c>
       <c r="B10" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,21 +1576,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1655,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687625</v>
+        <v>687514</v>
       </c>
       <c r="R10" t="n">
-        <v>7096144</v>
+        <v>7096131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,15 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124332782</v>
+        <v>124332740</v>
       </c>
       <c r="B11" t="n">
-        <v>90051</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,21 +1687,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1765,19 +1709,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687628</v>
+        <v>687507</v>
       </c>
       <c r="R11" t="n">
-        <v>7096143</v>
+        <v>7096131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1769,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,12 +1790,7 @@
         <v>124332744</v>
       </c>
       <c r="B12" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,15 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124332772</v>
+        <v>17225839</v>
       </c>
       <c r="B13" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,41 +1909,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687611</v>
+        <v>687326</v>
       </c>
       <c r="R13" t="n">
-        <v>7096125</v>
+        <v>7096120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,22 +1963,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,34 +1977,45 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124332738</v>
+        <v>124332745</v>
       </c>
       <c r="B14" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2127,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687514</v>
+        <v>687633</v>
       </c>
       <c r="R14" t="n">
-        <v>7096131</v>
+        <v>7096189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,15 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124332776</v>
+        <v>124332768</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2246,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687475</v>
+        <v>687485</v>
       </c>
       <c r="R15" t="n">
-        <v>7096137</v>
+        <v>7096168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,15 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124332731</v>
+        <v>124332779</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,21 +2249,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2357,16 +2271,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687535</v>
+        <v>687626</v>
       </c>
       <c r="R16" t="n">
-        <v>7096147</v>
+        <v>7096139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,6 +2334,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2435,15 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124332758</v>
+        <v>128912704</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,38 +2364,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687553</v>
+        <v>687774</v>
       </c>
       <c r="R17" t="n">
-        <v>7096128</v>
+        <v>7096150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,22 +2418,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,38 +2432,36 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>124332760</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2668,15 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124332740</v>
+        <v>128423068</v>
       </c>
       <c r="B19" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,38 +2576,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687507</v>
+        <v>687431</v>
       </c>
       <c r="R19" t="n">
-        <v>7096131</v>
+        <v>7096053</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,22 +2630,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,27 +2650,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124332780</v>
+        <v>128423069</v>
       </c>
       <c r="B20" t="n">
-        <v>92309</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2800,41 +2673,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687681</v>
+        <v>687381</v>
       </c>
       <c r="R20" t="n">
-        <v>7096188</v>
+        <v>7096073</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,22 +2727,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,73 +2741,63 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124332747</v>
+        <v>61258291</v>
       </c>
       <c r="B21" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Blåbergsheden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687633</v>
+        <v>687561</v>
       </c>
       <c r="R21" t="n">
-        <v>7096156</v>
+        <v>7096151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2978,22 +2824,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,66 +2844,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124332732</v>
+        <v>128397014</v>
       </c>
       <c r="B22" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687561</v>
+        <v>687582</v>
       </c>
       <c r="R22" t="n">
-        <v>7096151</v>
+        <v>7096036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,22 +2921,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,66 +2951,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124332742</v>
+        <v>128397032</v>
       </c>
       <c r="B23" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687577</v>
+        <v>687574</v>
       </c>
       <c r="R23" t="n">
-        <v>7096121</v>
+        <v>7096060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3210,22 +3028,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,69 +3058,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124332779</v>
+        <v>128397375</v>
       </c>
       <c r="B24" t="n">
-        <v>92287</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687626</v>
+        <v>687623</v>
       </c>
       <c r="R24" t="n">
-        <v>7096139</v>
+        <v>7096044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,22 +3135,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,19 +3159,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lukas Holmström, Ulf Hallin</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3375,11 +3180,11 @@
         <v>128423054</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3469,14 +3274,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128423063</v>
+        <v>128423055</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3504,10 +3309,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687549</v>
+        <v>687441</v>
       </c>
       <c r="R26" t="n">
-        <v>7095972</v>
+        <v>7096052</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3566,32 +3371,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128423068</v>
+        <v>128423056</v>
       </c>
       <c r="B27" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3601,10 +3406,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687431</v>
+        <v>687770</v>
       </c>
       <c r="R27" t="n">
-        <v>7096053</v>
+        <v>7095995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,21 +3461,21 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128423061</v>
+        <v>128423057</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3698,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687573</v>
+        <v>687752</v>
       </c>
       <c r="R28" t="n">
-        <v>7095996</v>
+        <v>7096003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,14 +3565,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128423065</v>
+        <v>128423058</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3795,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687544</v>
+        <v>687655</v>
       </c>
       <c r="R29" t="n">
-        <v>7095975</v>
+        <v>7096022</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,21 +3655,21 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128423057</v>
+        <v>128423059</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3892,10 +3697,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687752</v>
+        <v>687601</v>
       </c>
       <c r="R30" t="n">
-        <v>7096003</v>
+        <v>7096029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3954,32 +3759,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128423069</v>
+        <v>128423061</v>
       </c>
       <c r="B31" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3989,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687381</v>
+        <v>687573</v>
       </c>
       <c r="R31" t="n">
-        <v>7096073</v>
+        <v>7095996</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,21 +3849,21 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128423059</v>
+        <v>128423062</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4086,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687601</v>
+        <v>687564</v>
       </c>
       <c r="R32" t="n">
-        <v>7096029</v>
+        <v>7095983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,14 +3953,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128423056</v>
+        <v>128423063</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4183,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687770</v>
+        <v>687549</v>
       </c>
       <c r="R33" t="n">
-        <v>7095995</v>
+        <v>7095972</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4245,14 +4050,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128423058</v>
+        <v>128423064</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4280,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687655</v>
+        <v>687549</v>
       </c>
       <c r="R34" t="n">
-        <v>7096022</v>
+        <v>7095982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,21 +4140,21 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128423062</v>
+        <v>128423065</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4377,10 +4182,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687564</v>
+        <v>687544</v>
       </c>
       <c r="R35" t="n">
-        <v>7095983</v>
+        <v>7095975</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,21 +4237,21 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128397375</v>
+        <v>128423066</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4470,14 +4275,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687623</v>
+        <v>687511</v>
       </c>
       <c r="R36" t="n">
-        <v>7096044</v>
+        <v>7096024</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4507,19 +4312,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>19:46</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4534,44 +4329,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128423049</v>
+        <v>128423067</v>
       </c>
       <c r="B37" t="n">
-        <v>79648</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687529</v>
+        <v>687520</v>
       </c>
       <c r="R37" t="n">
-        <v>7096012</v>
+        <v>7096043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4636,21 +4431,21 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128423067</v>
+        <v>128912697</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4674,14 +4469,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>687520</v>
+        <v>687805</v>
       </c>
       <c r="R38" t="n">
-        <v>7096043</v>
+        <v>7095984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,12 +4503,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4728,26 +4523,30 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128423064</v>
+        <v>128912698</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4771,14 +4570,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>687549</v>
+        <v>687736</v>
       </c>
       <c r="R39" t="n">
-        <v>7095982</v>
+        <v>7096043</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4805,12 +4604,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4825,57 +4624,61 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128423053</v>
+        <v>128912699</v>
       </c>
       <c r="B40" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>687504</v>
+        <v>687675</v>
       </c>
       <c r="R40" t="n">
-        <v>7096055</v>
+        <v>7096065</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4902,12 +4705,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4922,57 +4725,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128423050</v>
+        <v>128912702</v>
       </c>
       <c r="B41" t="n">
-        <v>79648</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Einarstjärnen, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687474</v>
+        <v>687654</v>
       </c>
       <c r="R41" t="n">
-        <v>7096071</v>
+        <v>7096077</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4999,12 +4806,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,26 +4826,30 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128397032</v>
+        <v>128912703</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5062,14 +4873,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687574</v>
+        <v>687712</v>
       </c>
       <c r="R42" t="n">
-        <v>7096060</v>
+        <v>7096132</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5096,22 +4907,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,22 +4927,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>128423052</v>
       </c>
       <c r="B43" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,10 +5040,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128423055</v>
+        <v>128423053</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,21 +5051,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5270,10 +5075,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687441</v>
+        <v>687504</v>
       </c>
       <c r="R44" t="n">
-        <v>7096052</v>
+        <v>7096055</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,10 +5137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128397014</v>
+        <v>128423049</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,34 +5148,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbergssjöbäcken, Blåbergssjöbäcken, Ång</t>
+          <t>Einarstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687582</v>
+        <v>687529</v>
       </c>
       <c r="R45" t="n">
-        <v>7096036</v>
+        <v>7096012</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,19 +5205,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>19:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>19:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5427,22 +5222,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128423066</v>
+        <v>128423050</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,21 +5245,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5474,10 +5269,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>687511</v>
+        <v>687474</v>
       </c>
       <c r="R46" t="n">
-        <v>7096024</v>
+        <v>7096071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,17 +5324,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128912701</v>
+        <v>128912700</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,10 +5366,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687620</v>
+        <v>687674</v>
       </c>
       <c r="R47" t="n">
-        <v>7096086</v>
+        <v>7096063</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,10 +5432,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128912702</v>
+        <v>128912701</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,21 +5443,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5672,10 +5467,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687654</v>
+        <v>687620</v>
       </c>
       <c r="R48" t="n">
-        <v>7096077</v>
+        <v>7096086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5738,10 +5533,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128912698</v>
+        <v>133850817</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>93299</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,34 +5544,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6332770</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>687736</v>
+        <v>687471</v>
       </c>
       <c r="R49" t="n">
-        <v>7096043</v>
+        <v>7096139</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5803,12 +5598,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-64</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5817,32 +5617,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128912697</v>
+        <v>133850824</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>93299</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5850,34 +5647,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6332770</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>687805</v>
+        <v>687625</v>
       </c>
       <c r="R50" t="n">
-        <v>7095984</v>
+        <v>7096144</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,12 +5701,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,32 +5720,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128912704</v>
+        <v>133850825</v>
       </c>
       <c r="B51" t="n">
-        <v>92825</v>
+        <v>93299</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5951,34 +5750,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>6332770</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>687774</v>
+        <v>687515</v>
       </c>
       <c r="R51" t="n">
-        <v>7096150</v>
+        <v>7096129</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,12 +5804,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6019,32 +5823,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128912699</v>
+        <v>133850826</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>93299</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6052,34 +5853,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6332770</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>687675</v>
+        <v>687548</v>
       </c>
       <c r="R52" t="n">
-        <v>7096065</v>
+        <v>7096130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,12 +5907,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6120,32 +5926,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128912705</v>
+        <v>133850827</v>
       </c>
       <c r="B53" t="n">
-        <v>81029</v>
+        <v>93299</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,34 +5956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6332770</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687769</v>
+        <v>687553</v>
       </c>
       <c r="R53" t="n">
-        <v>7096150</v>
+        <v>7096117</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6207,12 +6010,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6221,32 +6029,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128912700</v>
+        <v>133850828</v>
       </c>
       <c r="B54" t="n">
-        <v>79663</v>
+        <v>93299</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,34 +6059,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6332770</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687674</v>
+        <v>687577</v>
       </c>
       <c r="R54" t="n">
-        <v>7096063</v>
+        <v>7096121</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6308,12 +6113,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6322,32 +6132,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128912703</v>
+        <v>133850829</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>93299</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6355,34 +6162,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6332770</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687712</v>
+        <v>687633</v>
       </c>
       <c r="R55" t="n">
-        <v>7096132</v>
+        <v>7096156</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6409,12 +6216,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6423,25 +6235,228 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133850833</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93299</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>687611</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7096125</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-48</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133850834</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93299</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>687475</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7096137</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20608-2023 artfynd.xlsx
+++ b/artfynd/A 20608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332782</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332780</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332730</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332732</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332744</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225839</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332745</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332768</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,6 +2425,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332779</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2451,6 +2531,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912704</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2562,6 +2647,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124332760</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,6 +2749,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423068</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2756,6 +2851,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423069</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2853,6 +2953,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61258291</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2960,6 +3065,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128397014</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3067,6 +3177,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128397032</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3174,6 +3289,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128397375</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3271,6 +3391,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423054</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3368,6 +3493,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423055</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423056</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,6 +3697,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423057</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3659,6 +3799,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423058</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3756,6 +3901,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423059</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3853,6 +4003,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423061</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3950,6 +4105,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423062</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4047,6 +4207,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423063</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4144,6 +4309,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423064</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4241,6 +4411,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423065</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4338,6 +4513,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423066</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4435,6 +4615,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423067</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4536,6 +4721,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912697</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4637,6 +4827,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912698</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4738,6 +4933,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912699</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4839,6 +5039,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912702</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4940,6 +5145,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912703</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5037,6 +5247,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423052</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5134,6 +5349,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423053</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5231,6 +5451,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423049</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5328,6 +5553,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423050</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5429,6 +5659,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912700</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5530,6 +5765,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912701</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5633,6 +5873,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850817</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5736,6 +5981,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850824</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5839,6 +6089,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850825</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5942,6 +6197,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850826</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6045,6 +6305,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850827</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6148,6 +6413,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850828</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6251,6 +6521,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850829</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6354,6 +6629,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850833</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6457,8 +6737,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>